--- a/product_selector_out/STM32F0 series - diff.xlsx
+++ b/product_selector_out/STM32F0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4523</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="18">
@@ -3348,18 +3348,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>25, 27</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3371,59 +3375,67 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>25, 27</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F031K4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>27 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>25, 27</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F031K4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -3435,18 +3447,18 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F031K4</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -3458,18 +3470,18 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -3481,18 +3493,18 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F051R4</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -3504,18 +3516,18 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F051R4</t>
+          <t>STM32F031K6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -3527,18 +3539,18 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32F051K6</t>
+          <t>STM32F031K6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -3550,18 +3562,18 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32F051K6</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -3573,18 +3585,18 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32F031F4</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -3596,18 +3608,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32F031F4</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -3619,18 +3631,18 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32F031F6</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -3642,18 +3654,18 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32F031F6</t>
+          <t>STM32F031F4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -3665,18 +3677,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32F031G4</t>
+          <t>STM32F031F4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -3688,18 +3700,18 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32F031G4</t>
+          <t>STM32F031F6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -3711,18 +3723,18 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32F031G6</t>
+          <t>STM32F031F6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -3734,18 +3746,18 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32F031G6</t>
+          <t>STM32F031G4</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -3757,18 +3769,18 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32F091VC</t>
+          <t>STM32F031G4</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -3780,18 +3792,18 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32F091VC</t>
+          <t>STM32F031G6</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -3803,18 +3815,18 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32F051C6</t>
+          <t>STM32F031G6</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -3826,18 +3838,18 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32F051C6</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -3849,18 +3861,18 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32F051T8</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -3872,18 +3884,18 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32F051T8</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -3895,18 +3907,18 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32F091RB</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -3918,18 +3930,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32F091RB</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -3941,18 +3953,18 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32F071C8</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -3964,18 +3976,18 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32F071C8</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -3987,18 +3999,18 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32F091RC</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -4010,18 +4022,18 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32F091RC</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -4033,18 +4045,18 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32F031C6</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -4056,18 +4068,18 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32F031C6</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -4079,18 +4091,18 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32F051K4</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4102,18 +4114,18 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32F051K4</t>
+          <t>STM32F031C6</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -4125,18 +4137,18 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32F031C4</t>
+          <t>STM32F031C6</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -4148,18 +4160,18 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32F031C4</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -4171,18 +4183,18 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32F071CB</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -4194,18 +4206,18 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32F071CB</t>
+          <t>STM32F031C4</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -4217,18 +4229,18 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32F091CB</t>
+          <t>STM32F031C4</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -4240,18 +4252,18 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32F091CB</t>
+          <t>STM32F071CB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -4260,8 +4272,77 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>STM32F071CB</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STM32F091CB</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>STM32F091CB</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E173"/>
+  <autoFilter ref="A18:E176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F0 series - diff.xlsx
+++ b/product_selector_out/STM32F0 series - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4672</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4522</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="18">
